--- a/data/trans_dic/P1435-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1435-Estudios-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,62</t>
+          <t>2,64; 4,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,73</t>
+          <t>0,68; 1,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,96</t>
+          <t>0,1; 0,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,51</t>
+          <t>0,81; 2,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,62</t>
+          <t>2,64; 4,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,73</t>
+          <t>0,68; 1,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,96</t>
+          <t>0,1; 0,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,51</t>
+          <t>0,81; 2,37</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 11,69</t>
+          <t>8,84; 11,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,43</t>
+          <t>4,19; 6,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,01</t>
+          <t>1,58; 2,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 18,73</t>
+          <t>5,69; 7,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 11,69</t>
+          <t>8,84; 11,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,43</t>
+          <t>4,19; 6,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,01</t>
+          <t>1,58; 2,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 18,73</t>
+          <t>5,69; 7,91</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,86</t>
+          <t>7,89; 13,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,27</t>
+          <t>4,27; 9,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,35</t>
+          <t>2,03; 5,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,83</t>
+          <t>8,11; 12,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,86</t>
+          <t>7,89; 13,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,27</t>
+          <t>4,27; 9,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,35</t>
+          <t>2,03; 5,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,83</t>
+          <t>8,11; 12,35</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,61</t>
+          <t>6,84; 8,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,55</t>
+          <t>3,29; 4,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,38</t>
+          <t>1,47; 2,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,31</t>
+          <t>5,37; 7,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,61</t>
+          <t>6,84; 8,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,55</t>
+          <t>3,29; 4,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,38</t>
+          <t>1,47; 2,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,31</t>
+          <t>5,37; 7,01</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11288</t>
         </is>
       </c>
     </row>
@@ -1231,42 +1231,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33330; 60768</t>
+          <t>34671; 60656</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8169; 23146</t>
+          <t>9144; 24202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>955; 9509</t>
+          <t>956; 9454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6208; 18870</t>
+          <t>6682; 19441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33330; 60768</t>
+          <t>34671; 60656</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8169; 23146</t>
+          <t>9144; 24202</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>955; 9509</t>
+          <t>956; 9454</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6208; 18870</t>
+          <t>6682; 19441</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189545</t>
+          <t>144311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>189545</t>
+          <t>144311</t>
         </is>
       </c>
     </row>
@@ -1379,42 +1379,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>140312; 185527</t>
+          <t>140408; 186841</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75223; 112865</t>
+          <t>73432; 112870</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32187; 59762</t>
+          <t>31476; 57285</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111121; 418143</t>
+          <t>123212; 171248</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>140312; 185527</t>
+          <t>140408; 186841</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75223; 112865</t>
+          <t>73432; 112870</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32187; 59762</t>
+          <t>31476; 57285</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>111121; 418143</t>
+          <t>123212; 171248</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66403</t>
+          <t>73333</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66403</t>
+          <t>73333</t>
         </is>
       </c>
     </row>
@@ -1527,42 +1527,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39220; 66021</t>
+          <t>37596; 65720</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20445; 42495</t>
+          <t>19569; 41751</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11454; 29396</t>
+          <t>11138; 28080</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52751; 84415</t>
+          <t>59200; 90183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39220; 66021</t>
+          <t>37596; 65720</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20445; 42495</t>
+          <t>19569; 41751</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11454; 29396</t>
+          <t>11138; 28080</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52751; 84415</t>
+          <t>59200; 90183</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
     </row>
@@ -1675,42 +1675,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>229865; 290809</t>
+          <t>231258; 290641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115768; 161531</t>
+          <t>116768; 162341</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53550; 84229</t>
+          <t>51813; 83600</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>187468; 484732</t>
+          <t>199788; 260517</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>229865; 290809</t>
+          <t>231258; 290641</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115768; 161531</t>
+          <t>116768; 162341</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53550; 84229</t>
+          <t>51813; 83600</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>187468; 484732</t>
+          <t>199788; 260517</t>
         </is>
       </c>
     </row>
